--- a/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6D0858-F262-4E10-AFE4-7752FF43F184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348AEF44-BC65-476A-8240-CFAC8CB1DE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -2194,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2342,6 +2342,116 @@
         <v>13.541944444444445</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>26374</v>
+      </c>
+      <c r="B12">
+        <v>439.56666666666666</v>
+      </c>
+      <c r="C12">
+        <v>7.3261111111111115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>86400</v>
+      </c>
+      <c r="B13">
+        <v>1440</v>
+      </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>53988</v>
+      </c>
+      <c r="B14">
+        <v>899.8</v>
+      </c>
+      <c r="C14">
+        <v>14.996666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>47586</v>
+      </c>
+      <c r="B15">
+        <v>793.1</v>
+      </c>
+      <c r="C15">
+        <v>13.218333333333334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>86400</v>
+      </c>
+      <c r="B16">
+        <v>1440</v>
+      </c>
+      <c r="C16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>86400</v>
+      </c>
+      <c r="B17">
+        <v>1440</v>
+      </c>
+      <c r="C17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>86400</v>
+      </c>
+      <c r="B18">
+        <v>1440</v>
+      </c>
+      <c r="C18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>46438</v>
+      </c>
+      <c r="B19">
+        <v>773.9666666666667</v>
+      </c>
+      <c r="C19">
+        <v>12.899444444444445</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>86400</v>
+      </c>
+      <c r="B20">
+        <v>1440</v>
+      </c>
+      <c r="C20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>48751</v>
+      </c>
+      <c r="B21">
+        <v>812.51666666666665</v>
+      </c>
+      <c r="C21">
+        <v>13.541944444444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348AEF44-BC65-476A-8240-CFAC8CB1DE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7737A4EF-B554-4663-B9C3-775443A8C28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -2194,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2452,6 +2452,556 @@
         <v>13.541944444444445</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>26374</v>
+      </c>
+      <c r="B22">
+        <v>439.56666666666666</v>
+      </c>
+      <c r="C22">
+        <v>7.3261111111111115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>86400</v>
+      </c>
+      <c r="B23">
+        <v>1440</v>
+      </c>
+      <c r="C23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>53988</v>
+      </c>
+      <c r="B24">
+        <v>899.8</v>
+      </c>
+      <c r="C24">
+        <v>14.996666666666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>47586</v>
+      </c>
+      <c r="B25">
+        <v>793.1</v>
+      </c>
+      <c r="C25">
+        <v>13.218333333333334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>86400</v>
+      </c>
+      <c r="B26">
+        <v>1440</v>
+      </c>
+      <c r="C26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>86400</v>
+      </c>
+      <c r="B27">
+        <v>1440</v>
+      </c>
+      <c r="C27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>86400</v>
+      </c>
+      <c r="B28">
+        <v>1440</v>
+      </c>
+      <c r="C28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>46438</v>
+      </c>
+      <c r="B29">
+        <v>773.9666666666667</v>
+      </c>
+      <c r="C29">
+        <v>12.899444444444445</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>86400</v>
+      </c>
+      <c r="B30">
+        <v>1440</v>
+      </c>
+      <c r="C30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>48751</v>
+      </c>
+      <c r="B31">
+        <v>812.51666666666665</v>
+      </c>
+      <c r="C31">
+        <v>13.541944444444445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>38091</v>
+      </c>
+      <c r="B32">
+        <v>634.85</v>
+      </c>
+      <c r="C32">
+        <v>10.580833333333333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>86400</v>
+      </c>
+      <c r="B33">
+        <v>1440</v>
+      </c>
+      <c r="C33">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>52209</v>
+      </c>
+      <c r="B34">
+        <v>870.15</v>
+      </c>
+      <c r="C34">
+        <v>14.5025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>29675</v>
+      </c>
+      <c r="B35">
+        <v>494.58333333333331</v>
+      </c>
+      <c r="C35">
+        <v>8.2430555555555554</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>86400</v>
+      </c>
+      <c r="B36">
+        <v>1440</v>
+      </c>
+      <c r="C36">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>86400</v>
+      </c>
+      <c r="B37">
+        <v>1440</v>
+      </c>
+      <c r="C37">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>56673</v>
+      </c>
+      <c r="B38">
+        <v>944.55</v>
+      </c>
+      <c r="C38">
+        <v>15.7425</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>50545</v>
+      </c>
+      <c r="B39">
+        <v>842.41666666666663</v>
+      </c>
+      <c r="C39">
+        <v>14.040277777777778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>26966</v>
+      </c>
+      <c r="B40">
+        <v>449.43333333333334</v>
+      </c>
+      <c r="C40">
+        <v>7.4905555555555559</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>86400</v>
+      </c>
+      <c r="B41">
+        <v>1440</v>
+      </c>
+      <c r="C41">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>86400</v>
+      </c>
+      <c r="B42">
+        <v>1440</v>
+      </c>
+      <c r="C42">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>67038</v>
+      </c>
+      <c r="B43">
+        <v>1117.3</v>
+      </c>
+      <c r="C43">
+        <v>18.621666666666666</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>22416</v>
+      </c>
+      <c r="B44">
+        <v>373.6</v>
+      </c>
+      <c r="C44">
+        <v>6.2266666666666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>20177</v>
+      </c>
+      <c r="B45">
+        <v>336.28333333333336</v>
+      </c>
+      <c r="C45">
+        <v>5.6047222222222226</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>49079</v>
+      </c>
+      <c r="B46">
+        <v>817.98333333333335</v>
+      </c>
+      <c r="C46">
+        <v>13.633055555555556</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>53715</v>
+      </c>
+      <c r="B47">
+        <v>895.25</v>
+      </c>
+      <c r="C47">
+        <v>14.920833333333333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>25876</v>
+      </c>
+      <c r="B48">
+        <v>431.26666666666665</v>
+      </c>
+      <c r="C48">
+        <v>7.1877777777777778</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>20972</v>
+      </c>
+      <c r="B49">
+        <v>349.53333333333336</v>
+      </c>
+      <c r="C49">
+        <v>5.8255555555555558</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>86400</v>
+      </c>
+      <c r="B50">
+        <v>1440</v>
+      </c>
+      <c r="C50">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>37552</v>
+      </c>
+      <c r="B51">
+        <v>625.86666666666667</v>
+      </c>
+      <c r="C51">
+        <v>10.431111111111111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>28495</v>
+      </c>
+      <c r="B52">
+        <v>474.91666666666669</v>
+      </c>
+      <c r="C52">
+        <v>7.9152777777777779</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>35100</v>
+      </c>
+      <c r="B53">
+        <v>585</v>
+      </c>
+      <c r="C53">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>28420</v>
+      </c>
+      <c r="B54">
+        <v>473.66666666666669</v>
+      </c>
+      <c r="C54">
+        <v>7.8944444444444448</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>86400</v>
+      </c>
+      <c r="B55">
+        <v>1440</v>
+      </c>
+      <c r="C55">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>86400</v>
+      </c>
+      <c r="B56">
+        <v>1440</v>
+      </c>
+      <c r="C56">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>86400</v>
+      </c>
+      <c r="B57">
+        <v>1440</v>
+      </c>
+      <c r="C57">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>86400</v>
+      </c>
+      <c r="B58">
+        <v>1440</v>
+      </c>
+      <c r="C58">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>38714</v>
+      </c>
+      <c r="B59">
+        <v>645.23333333333335</v>
+      </c>
+      <c r="C59">
+        <v>10.753888888888889</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>86400</v>
+      </c>
+      <c r="B60">
+        <v>1440</v>
+      </c>
+      <c r="C60">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>84518</v>
+      </c>
+      <c r="B61">
+        <v>1408.6333333333334</v>
+      </c>
+      <c r="C61">
+        <v>23.477222222222224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>86400</v>
+      </c>
+      <c r="B62">
+        <v>1440</v>
+      </c>
+      <c r="C62">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>73480</v>
+      </c>
+      <c r="B63">
+        <v>1224.6666666666667</v>
+      </c>
+      <c r="C63">
+        <v>20.411111111111111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>52707</v>
+      </c>
+      <c r="B64">
+        <v>878.45</v>
+      </c>
+      <c r="C64">
+        <v>14.640833333333333</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>47221</v>
+      </c>
+      <c r="B65">
+        <v>787.01666666666665</v>
+      </c>
+      <c r="C65">
+        <v>13.116944444444444</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>72861</v>
+      </c>
+      <c r="B66">
+        <v>1214.3499999999999</v>
+      </c>
+      <c r="C66">
+        <v>20.239166666666666</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>26120</v>
+      </c>
+      <c r="B67">
+        <v>435.33333333333331</v>
+      </c>
+      <c r="C67">
+        <v>7.2555555555555555</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>75130</v>
+      </c>
+      <c r="B68">
+        <v>1252.1666666666667</v>
+      </c>
+      <c r="C68">
+        <v>20.869444444444444</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>83591</v>
+      </c>
+      <c r="B69">
+        <v>1393.1833333333334</v>
+      </c>
+      <c r="C69">
+        <v>23.219722222222224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>20854</v>
+      </c>
+      <c r="B70">
+        <v>347.56666666666666</v>
+      </c>
+      <c r="C70">
+        <v>5.7927777777777774</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>43004</v>
+      </c>
+      <c r="B71">
+        <v>716.73333333333335</v>
+      </c>
+      <c r="C71">
+        <v>11.945555555555556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7737A4EF-B554-4663-B9C3-775443A8C28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8542788-F16D-4C14-AAA3-CB92B1273380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -2194,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -3002,6 +3002,226 @@
         <v>11.945555555555556</v>
       </c>
     </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>26374</v>
+      </c>
+      <c r="B72">
+        <v>439.56666666666666</v>
+      </c>
+      <c r="C72">
+        <v>7.3261111111111115</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>86400</v>
+      </c>
+      <c r="B73">
+        <v>1440</v>
+      </c>
+      <c r="C73">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>53988</v>
+      </c>
+      <c r="B74">
+        <v>899.8</v>
+      </c>
+      <c r="C74">
+        <v>14.996666666666666</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>47586</v>
+      </c>
+      <c r="B75">
+        <v>793.1</v>
+      </c>
+      <c r="C75">
+        <v>13.218333333333334</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>86400</v>
+      </c>
+      <c r="B76">
+        <v>1440</v>
+      </c>
+      <c r="C76">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>86400</v>
+      </c>
+      <c r="B77">
+        <v>1440</v>
+      </c>
+      <c r="C77">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>86400</v>
+      </c>
+      <c r="B78">
+        <v>1440</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>46438</v>
+      </c>
+      <c r="B79">
+        <v>773.9666666666667</v>
+      </c>
+      <c r="C79">
+        <v>12.899444444444445</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>86400</v>
+      </c>
+      <c r="B80">
+        <v>1440</v>
+      </c>
+      <c r="C80">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>48751</v>
+      </c>
+      <c r="B81">
+        <v>812.51666666666665</v>
+      </c>
+      <c r="C81">
+        <v>13.541944444444445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>38091</v>
+      </c>
+      <c r="B82">
+        <v>634.85</v>
+      </c>
+      <c r="C82">
+        <v>10.580833333333333</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>86400</v>
+      </c>
+      <c r="B83">
+        <v>1440</v>
+      </c>
+      <c r="C83">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>52209</v>
+      </c>
+      <c r="B84">
+        <v>870.15</v>
+      </c>
+      <c r="C84">
+        <v>14.5025</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>29675</v>
+      </c>
+      <c r="B85">
+        <v>494.58333333333331</v>
+      </c>
+      <c r="C85">
+        <v>8.2430555555555554</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>86400</v>
+      </c>
+      <c r="B86">
+        <v>1440</v>
+      </c>
+      <c r="C86">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86400</v>
+      </c>
+      <c r="B87">
+        <v>1440</v>
+      </c>
+      <c r="C87">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>56673</v>
+      </c>
+      <c r="B88">
+        <v>944.55</v>
+      </c>
+      <c r="C88">
+        <v>15.7425</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>50545</v>
+      </c>
+      <c r="B89">
+        <v>842.41666666666663</v>
+      </c>
+      <c r="C89">
+        <v>14.040277777777778</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>26966</v>
+      </c>
+      <c r="B90">
+        <v>449.43333333333334</v>
+      </c>
+      <c r="C90">
+        <v>7.4905555555555559</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>86400</v>
+      </c>
+      <c r="B91">
+        <v>1440</v>
+      </c>
+      <c r="C91">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8542788-F16D-4C14-AAA3-CB92B1273380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AE97BA-350D-415C-A8A2-1470A6517989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="5085" yWindow="1035" windowWidth="18675" windowHeight="12975" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
@@ -426,473 +426,743 @@
       <c r="A2">
         <v>19232</v>
       </c>
+      <c r="B2">
+        <v>26374</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11287</v>
       </c>
+      <c r="B3">
+        <v>86400</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>21931</v>
       </c>
+      <c r="B4">
+        <v>53988</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>19650</v>
       </c>
+      <c r="B5">
+        <v>47586</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26696</v>
       </c>
+      <c r="B6">
+        <v>86400</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>17714</v>
       </c>
+      <c r="B7">
+        <v>86400</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25094</v>
       </c>
+      <c r="B8">
+        <v>86400</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>28007</v>
       </c>
+      <c r="B9">
+        <v>46438</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>18679</v>
       </c>
+      <c r="B10">
+        <v>86400</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>19643</v>
       </c>
+      <c r="B11">
+        <v>48751</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>19232</v>
       </c>
+      <c r="B12">
+        <v>26374</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11287</v>
       </c>
+      <c r="B13">
+        <v>86400</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>21931</v>
       </c>
+      <c r="B14">
+        <v>53988</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>19650</v>
       </c>
+      <c r="B15">
+        <v>47586</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26696</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17714</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25094</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>28007</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18679</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19643</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>48751</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21265</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>26374</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21377</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22322</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>53988</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24275</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>47586</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>30816</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>16545</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>19903</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>39176</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>21530</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>21976</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>48751</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>24713</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>38091</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>23243</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21561</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>52209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>21740</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>29675</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>18463</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>17179</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>24412</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>56673</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>26431</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>50545</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>23323</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>26966</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>26872</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>19027</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>28879</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>67038</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>18884</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>22416</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>20187</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>20177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>36209</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>49079</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>21322</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>53715</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>26316</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>25876</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>19711</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>20972</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>24521</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>28146</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>37552</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>18798</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>28495</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>28569</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>35100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>25077</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>28420</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>29094</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>24085</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>19852</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>21048</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>17948</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>38714</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>16730</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>22241</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>84518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>12174</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>28310</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>73480</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>19955</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>52707</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>22235</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>47221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>18482</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>72861</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>16728</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>26120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>13341</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <v>75130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>20871</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>83591</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>29148</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>20854</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>19996</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>43004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>21397</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>26374</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>19346</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>24691</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B74">
+        <v>53988</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>20727</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B75">
+        <v>47586</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>19232</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B76">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>11287</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>21931</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>19650</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>26696</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B80">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>17714</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>48751</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>19232</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B82">
+        <v>38091</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>11287</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B83">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>21931</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B84">
+        <v>52209</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>19650</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B85">
+        <v>29675</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>17714</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B86">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>25094</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>28007</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>56673</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>18679</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B89">
+        <v>50545</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>19643</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>26966</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>21265</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>21377</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>22322</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>16545</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>19903</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>21530</v>
       </c>

--- a/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Time_for_Bac_Fix_MutRate_Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 3 - SOS vs Random Mutation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AE97BA-350D-415C-A8A2-1470A6517989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EF2D97-32D6-4732-9710-1C73323758AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="1035" windowWidth="18675" windowHeight="12975" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
@@ -1146,50 +1146,80 @@
       <c r="A92">
         <v>21377</v>
       </c>
+      <c r="B92">
+        <v>26374</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>22322</v>
       </c>
+      <c r="B93">
+        <v>86400</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>16545</v>
       </c>
+      <c r="B94">
+        <v>53988</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>19903</v>
       </c>
+      <c r="B95">
+        <v>47586</v>
+      </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>21530</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>21976</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>23243</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>21561</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>21740</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>18463</v>
+      </c>
+      <c r="B101">
+        <v>48751</v>
       </c>
     </row>
   </sheetData>
@@ -2464,7 +2494,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -3492,6 +3522,116 @@
         <v>24</v>
       </c>
     </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>26374</v>
+      </c>
+      <c r="B92">
+        <v>439.56666666666666</v>
+      </c>
+      <c r="C92">
+        <v>7.3261111111111115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>86400</v>
+      </c>
+      <c r="B93">
+        <v>1440</v>
+      </c>
+      <c r="C93">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>53988</v>
+      </c>
+      <c r="B94">
+        <v>899.8</v>
+      </c>
+      <c r="C94">
+        <v>14.996666666666666</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>47586</v>
+      </c>
+      <c r="B95">
+        <v>793.1</v>
+      </c>
+      <c r="C95">
+        <v>13.218333333333334</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>86400</v>
+      </c>
+      <c r="B96">
+        <v>1440</v>
+      </c>
+      <c r="C96">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>86400</v>
+      </c>
+      <c r="B97">
+        <v>1440</v>
+      </c>
+      <c r="C97">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>86400</v>
+      </c>
+      <c r="B98">
+        <v>1440</v>
+      </c>
+      <c r="C98">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>46438</v>
+      </c>
+      <c r="B99">
+        <v>773.9666666666667</v>
+      </c>
+      <c r="C99">
+        <v>12.899444444444445</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>86400</v>
+      </c>
+      <c r="B100">
+        <v>1440</v>
+      </c>
+      <c r="C100">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>48751</v>
+      </c>
+      <c r="B101">
+        <v>812.51666666666665</v>
+      </c>
+      <c r="C101">
+        <v>13.541944444444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
